--- a/public/templates/forms/A-033-RiskTreatmentAcceptanceDecisionsLog-FORM.xlsx
+++ b/public/templates/forms/A-033-RiskTreatmentAcceptanceDecisionsLog-FORM.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="13">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -325,7 +325,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -359,7 +359,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/forms/A-033-RiskTreatmentAcceptanceDecisionsLog-FORM.xlsx
+++ b/public/templates/forms/A-033-RiskTreatmentAcceptanceDecisionsLog-FORM.xlsx
@@ -4,20 +4,25 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Form!$12:$12</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="13">
     <font>
       <name val="Aptos"/>
@@ -151,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -205,6 +210,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,7 +577,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -714,7 +722,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Risk ID</t>
@@ -890,7 +898,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
+    <row r="28" ht="34.7" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Risk ID</t>
@@ -1123,7 +1131,8 @@
       <formula1>"Mitigate,Accept,Transfer,Avoid"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1131,7 +1140,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1222,7 +1231,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Decision</t>
@@ -1244,7 +1253,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Rationale</t>
@@ -1266,7 +1275,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Decision Authority</t>
@@ -1304,10 +1313,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
+      <c r="D10" s="22">
+        <v>46114</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -1326,10 +1333,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>2027-04-02</t>
-        </is>
+      <c r="D11" s="22">
+        <v>46479</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1427,6 +1432,7 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>